--- a/JsonConverter/ExcelFiles/Monster.xlsx
+++ b/JsonConverter/ExcelFiles/Monster.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <r>
       <rPr>
@@ -88,6 +88,98 @@
   <si>
     <t xml:space="preserve">Mob_Hyena</t>
   </si>
+  <si>
+    <t xml:space="preserve">Monster_BlueSlime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueSlime</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mob_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">BlueSlime</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_WareWolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WareWolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mob_WareWolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_Ork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mob_Ork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_Pharaoh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharaoh</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mob_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Pharaoh</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_LittleDevil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LittleDevil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mob_LittleDevil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mob_Knight</t>
+  </si>
 </sst>
 </file>
 
@@ -96,7 +188,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -142,6 +234,13 @@
       <name val="&quot;맑은 고딕&quot;"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -212,7 +311,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -242,6 +341,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -498,7 +601,8 @@
   <dimension ref="A1:L123"/>
   <sheetFormatPr defaultColWidth="12.7578125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="1" style="1" width="15.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="20.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="1" width="15.46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -542,9 +646,7 @@
       <c r="H2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="I2" s="4"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -568,13 +670,13 @@
       <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="H3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
@@ -590,104 +692,200 @@
         <v>15</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="6"/>
+        <v>100</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="H4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
+    <row r="5" customFormat="false" ht="16.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
+      <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="A7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+    <row r="8" customFormat="false" ht="16.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="A9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
+      <c r="A10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>350</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>350</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -2010,232 +2208,232 @@
       <c r="L104" s="6"/>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="7"/>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7"/>
-      <c r="I105" s="7"/>
-      <c r="L105" s="7"/>
+      <c r="A105" s="8"/>
+      <c r="B105" s="8"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="8"/>
+      <c r="L105" s="8"/>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="7"/>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="7"/>
-      <c r="I106" s="7"/>
-      <c r="L106" s="7"/>
+      <c r="A106" s="8"/>
+      <c r="B106" s="8"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="8"/>
+      <c r="L106" s="8"/>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="7"/>
-      <c r="B107" s="7"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
-      <c r="I107" s="7"/>
-      <c r="L107" s="7"/>
+      <c r="A107" s="8"/>
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="8"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="8"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="8"/>
+      <c r="L107" s="8"/>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="7"/>
-      <c r="B108" s="7"/>
-      <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="7"/>
-      <c r="H108" s="7"/>
-      <c r="I108" s="7"/>
-      <c r="L108" s="7"/>
+      <c r="A108" s="8"/>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="8"/>
+      <c r="L108" s="8"/>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="7"/>
-      <c r="I109" s="7"/>
-      <c r="L109" s="7"/>
+      <c r="A109" s="8"/>
+      <c r="B109" s="8"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8"/>
+      <c r="F109" s="8"/>
+      <c r="G109" s="8"/>
+      <c r="H109" s="8"/>
+      <c r="I109" s="8"/>
+      <c r="L109" s="8"/>
     </row>
     <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7"/>
-      <c r="B110" s="7"/>
-      <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-      <c r="G110" s="7"/>
-      <c r="H110" s="7"/>
-      <c r="I110" s="7"/>
-      <c r="L110" s="7"/>
+      <c r="A110" s="8"/>
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="8"/>
+      <c r="F110" s="8"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="8"/>
+      <c r="L110" s="8"/>
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="7"/>
-      <c r="B111" s="7"/>
-      <c r="C111" s="7"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="7"/>
-      <c r="I111" s="7"/>
-      <c r="L111" s="7"/>
+      <c r="A111" s="8"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="8"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="8"/>
+      <c r="L111" s="8"/>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="7"/>
-      <c r="B112" s="7"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-      <c r="H112" s="7"/>
-      <c r="I112" s="7"/>
-      <c r="L112" s="7"/>
+      <c r="A112" s="8"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="8"/>
+      <c r="G112" s="8"/>
+      <c r="H112" s="8"/>
+      <c r="I112" s="8"/>
+      <c r="L112" s="8"/>
     </row>
     <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="7"/>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
-      <c r="I113" s="7"/>
-      <c r="L113" s="7"/>
+      <c r="A113" s="8"/>
+      <c r="B113" s="8"/>
+      <c r="C113" s="8"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="8"/>
+      <c r="G113" s="8"/>
+      <c r="H113" s="8"/>
+      <c r="I113" s="8"/>
+      <c r="L113" s="8"/>
     </row>
     <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="7"/>
-      <c r="B114" s="7"/>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
-      <c r="G114" s="7"/>
-      <c r="H114" s="7"/>
-      <c r="I114" s="7"/>
-      <c r="L114" s="7"/>
+      <c r="A114" s="8"/>
+      <c r="B114" s="8"/>
+      <c r="C114" s="8"/>
+      <c r="D114" s="8"/>
+      <c r="E114" s="8"/>
+      <c r="F114" s="8"/>
+      <c r="G114" s="8"/>
+      <c r="H114" s="8"/>
+      <c r="I114" s="8"/>
+      <c r="L114" s="8"/>
     </row>
     <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="7"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-      <c r="G115" s="7"/>
-      <c r="H115" s="7"/>
-      <c r="I115" s="7"/>
-      <c r="L115" s="7"/>
+      <c r="A115" s="8"/>
+      <c r="B115" s="8"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="8"/>
+      <c r="G115" s="8"/>
+      <c r="H115" s="8"/>
+      <c r="I115" s="8"/>
+      <c r="L115" s="8"/>
     </row>
     <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="7"/>
-      <c r="B116" s="7"/>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
-      <c r="I116" s="7"/>
-      <c r="L116" s="7"/>
+      <c r="A116" s="8"/>
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="8"/>
+      <c r="E116" s="8"/>
+      <c r="F116" s="8"/>
+      <c r="G116" s="8"/>
+      <c r="H116" s="8"/>
+      <c r="I116" s="8"/>
+      <c r="L116" s="8"/>
     </row>
     <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="7"/>
-      <c r="B117" s="7"/>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="7"/>
-      <c r="I117" s="7"/>
-      <c r="L117" s="7"/>
+      <c r="A117" s="8"/>
+      <c r="B117" s="8"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="8"/>
+      <c r="G117" s="8"/>
+      <c r="H117" s="8"/>
+      <c r="I117" s="8"/>
+      <c r="L117" s="8"/>
     </row>
     <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="7"/>
-      <c r="B118" s="7"/>
-      <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="7"/>
-      <c r="H118" s="7"/>
-      <c r="I118" s="7"/>
-      <c r="L118" s="7"/>
+      <c r="A118" s="8"/>
+      <c r="B118" s="8"/>
+      <c r="C118" s="8"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="8"/>
+      <c r="G118" s="8"/>
+      <c r="H118" s="8"/>
+      <c r="I118" s="8"/>
+      <c r="L118" s="8"/>
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="7"/>
-      <c r="B119" s="7"/>
-      <c r="C119" s="7"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="7"/>
-      <c r="F119" s="7"/>
-      <c r="G119" s="7"/>
-      <c r="H119" s="7"/>
-      <c r="I119" s="7"/>
-      <c r="L119" s="7"/>
+      <c r="A119" s="8"/>
+      <c r="B119" s="8"/>
+      <c r="C119" s="8"/>
+      <c r="D119" s="8"/>
+      <c r="E119" s="8"/>
+      <c r="F119" s="8"/>
+      <c r="G119" s="8"/>
+      <c r="H119" s="8"/>
+      <c r="I119" s="8"/>
+      <c r="L119" s="8"/>
     </row>
     <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="7"/>
-      <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="7"/>
-      <c r="H120" s="7"/>
-      <c r="I120" s="7"/>
-      <c r="L120" s="7"/>
+      <c r="A120" s="8"/>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
+      <c r="I120" s="8"/>
+      <c r="L120" s="8"/>
     </row>
     <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="7"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
-      <c r="G121" s="7"/>
-      <c r="H121" s="7"/>
-      <c r="I121" s="7"/>
-      <c r="L121" s="7"/>
+      <c r="A121" s="8"/>
+      <c r="B121" s="8"/>
+      <c r="C121" s="8"/>
+      <c r="D121" s="8"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="8"/>
+      <c r="G121" s="8"/>
+      <c r="H121" s="8"/>
+      <c r="I121" s="8"/>
+      <c r="L121" s="8"/>
     </row>
     <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="7"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="7"/>
-      <c r="H122" s="7"/>
-      <c r="I122" s="7"/>
-      <c r="L122" s="7"/>
+      <c r="A122" s="8"/>
+      <c r="B122" s="8"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="8"/>
+      <c r="E122" s="8"/>
+      <c r="F122" s="8"/>
+      <c r="G122" s="8"/>
+      <c r="H122" s="8"/>
+      <c r="I122" s="8"/>
+      <c r="L122" s="8"/>
     </row>
     <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="7"/>
-      <c r="B123" s="7"/>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7"/>
-      <c r="G123" s="7"/>
-      <c r="H123" s="7"/>
-      <c r="I123" s="7"/>
-      <c r="L123" s="7"/>
+      <c r="A123" s="8"/>
+      <c r="B123" s="8"/>
+      <c r="C123" s="8"/>
+      <c r="D123" s="8"/>
+      <c r="E123" s="8"/>
+      <c r="F123" s="8"/>
+      <c r="G123" s="8"/>
+      <c r="H123" s="8"/>
+      <c r="I123" s="8"/>
+      <c r="L123" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/JsonConverter/ExcelFiles/Monster.xlsx
+++ b/JsonConverter/ExcelFiles/Monster.xlsx
@@ -701,10 +701,10 @@
         <v>100</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
@@ -731,10 +731,10 @@
         <v>50</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
@@ -761,10 +761,10 @@
         <v>150</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
@@ -791,10 +791,10 @@
         <v>200</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -821,10 +821,10 @@
         <v>250</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
@@ -851,10 +851,10 @@
         <v>300</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
@@ -881,10 +881,10 @@
         <v>350</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.5</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
